--- a/ML_SSW_2025/MedicionesSueloCeramica2024/secondary_TOF_results.xlsx
+++ b/ML_SSW_2025/MedicionesSueloCeramica2024/secondary_TOF_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pablo\Desktop\InvestigacionUSFQ\SSWCompleteAnalysis\SingleSolitaryWaveAnalysis\ML_SSW_2025\MedicionesSueloCeramica2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E068B66-FB46-4844-87F6-3D20AB6EB966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F73339A-0AFF-436B-8014-60FB5BAA5256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -163,7 +163,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1603,12 +1603,12 @@
         <v>1.4200142001410399E-3</v>
       </c>
       <c r="N31">
-        <f>AVERAGE(L31:L35)</f>
-        <v>2.6791019070752902</v>
+        <f>AVERAGE(L31:L34)</f>
+        <v>2.8853393323793255</v>
       </c>
       <c r="O31" s="2">
         <f>AVERAGE(M31:M35)</f>
-        <v>1.4075140751388382E-3</v>
+        <v>1.4133474668067691E-3</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.45">
@@ -1651,7 +1651,7 @@
         <v>1.4200142001392635E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>1.4000140001400041E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1722,16 +1722,9 @@
       <c r="J34">
         <v>8.6000860008539348E-4</v>
       </c>
-      <c r="L34">
-        <f t="shared" si="0"/>
-        <v>2.0603896311631846</v>
-      </c>
-      <c r="M34" s="2">
-        <f t="shared" si="2"/>
-        <v>1.3900139001350453E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -1764,12 +1757,12 @@
       </c>
       <c r="M35" s="2"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -1800,16 +1793,17 @@
       <c r="J37">
         <v>5.8000580006023483E-4</v>
       </c>
-      <c r="L37">
-        <f t="shared" si="0"/>
-        <v>2.1667835931200519</v>
-      </c>
-      <c r="M37" s="2">
-        <f t="shared" si="2"/>
-        <v>1.3300133001301617E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M37" s="2"/>
+      <c r="N37">
+        <f>AVERAGE(L37:L41)</f>
+        <v>1.7903215026200612</v>
+      </c>
+      <c r="O37">
+        <f>AVERAGE(M37:M41)</f>
+        <v>1.2650126501281278E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -1849,7 +1843,7 @@
         <v>1.2800128001231315E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1889,7 +1883,7 @@
         <v>1.2700127001323835E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1929,7 +1923,7 @@
         <v>1.2500125001295714E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -1969,12 +1963,12 @@
         <v>1.2600126001274248E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -2013,8 +2007,16 @@
         <f t="shared" si="2"/>
         <v>1.4100141001449629E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N43">
+        <f>AVERAGE(L43:L47)</f>
+        <v>1.685209082640706</v>
+      </c>
+      <c r="O43">
+        <f>AVERAGE(M43:M47)</f>
+        <v>1.4500145001458502E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -2045,16 +2047,9 @@
       <c r="J44">
         <v>3.8000380004632461E-4</v>
       </c>
-      <c r="L44">
-        <f t="shared" si="0"/>
-        <v>1.9481438463407204</v>
-      </c>
-      <c r="M44" s="2">
-        <f t="shared" si="2"/>
-        <v>1.4000140001257932E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -2085,16 +2080,9 @@
       <c r="J45">
         <v>4.2000420003773797E-4</v>
       </c>
-      <c r="L45">
-        <f t="shared" si="0"/>
-        <v>2.1525618192199851</v>
-      </c>
-      <c r="M45" s="2">
-        <f t="shared" si="2"/>
-        <v>1.3700137001535495E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -2134,7 +2122,7 @@
         <v>1.4200142001357108E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -2174,12 +2162,12 @@
         <v>1.5200152001568767E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -2218,8 +2206,16 @@
         <f t="shared" si="2"/>
         <v>1.4800148001476998E-3</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N49">
+        <f>AVERAGE(L49:L55)</f>
+        <v>1.9067806955784921</v>
+      </c>
+      <c r="O49">
+        <f>AVERAGE(M49:M55)</f>
+        <v>1.5250152501528429E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -2250,16 +2246,9 @@
       <c r="J50">
         <v>6.5000650005941907E-4</v>
       </c>
-      <c r="L50">
-        <f t="shared" si="0"/>
-        <v>0.95684910333545647</v>
-      </c>
-      <c r="M50" s="2">
-        <f t="shared" si="2"/>
-        <v>4.8000480005327972E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -2299,7 +2288,7 @@
         <v>1.5200152001497713E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -2339,7 +2328,7 @@
         <v>1.5000150001611701E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -2379,7 +2368,7 @@
         <v>1.510015100151918E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -2419,7 +2408,7 @@
         <v>1.5700157001532489E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -2459,12 +2448,12 @@
         <v>1.5700157001532489E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>10</v>
       </c>
@@ -2503,8 +2492,16 @@
         <f t="shared" si="2"/>
         <v>1.2500125001260187E-3</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N57">
+        <f>AVERAGE(L57:L61)</f>
+        <v>1.9971672054777752</v>
+      </c>
+      <c r="O57" s="2">
+        <f>AVERAGE(M57:M61)</f>
+        <v>1.2375123751242612E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>10</v>
       </c>
@@ -2544,7 +2541,7 @@
         <v>1.2200122001218006E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>10</v>
       </c>
@@ -2584,7 +2581,7 @@
         <v>1.2400124001246127E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -2624,7 +2621,7 @@
         <v>1.2400124001246127E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>10</v>
       </c>
@@ -2655,21 +2652,14 @@
       <c r="J61">
         <v>5.000050000489864E-4</v>
       </c>
-      <c r="L61">
-        <f t="shared" si="0"/>
-        <v>1.5430887189397569</v>
-      </c>
-      <c r="M61" s="2">
-        <f t="shared" si="2"/>
-        <v>1.2400124001246127E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -2700,16 +2690,17 @@
       <c r="J63">
         <v>6.800068000689663E-4</v>
       </c>
-      <c r="L63">
-        <f t="shared" si="0"/>
-        <v>2.0509439689996047</v>
-      </c>
-      <c r="M63" s="2">
-        <f t="shared" si="2"/>
-        <v>1.7400174001735991E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M63" s="2"/>
+      <c r="N63">
+        <f>AVERAGE(L63:L67)</f>
+        <v>1.3945819157578629</v>
+      </c>
+      <c r="O63" s="2">
+        <f>AVERAGE(M63:M67)</f>
+        <v>1.6266829334909971E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -2740,16 +2731,9 @@
       <c r="J64">
         <v>4.8000480003906887E-4</v>
       </c>
-      <c r="L64">
-        <f t="shared" si="0"/>
-        <v>1.9264514539064546</v>
-      </c>
-      <c r="M64" s="2">
-        <f t="shared" si="2"/>
-        <v>1.6400164001737494E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M64" s="2"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -2789,7 +2773,7 @@
         <v>1.6200162001638319E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -2829,7 +2813,7 @@
         <v>1.620016200149621E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -2869,12 +2853,12 @@
         <v>1.6400164001595385E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -2913,8 +2897,16 @@
         <f t="shared" si="2"/>
         <v>1.4800148001476998E-3</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N69">
+        <f>AVERAGE(L69:L73)</f>
+        <v>2.254059142722955</v>
+      </c>
+      <c r="O69" s="2">
+        <f>AVERAGE(M69:M73)</f>
+        <v>1.4550145501450729E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -2954,7 +2946,7 @@
         <v>1.4200142001428162E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -2994,7 +2986,7 @@
         <v>1.4600146001484404E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -3034,12 +3026,12 @@
         <v>1.460014600141335E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -3070,16 +3062,17 @@
       <c r="J74">
         <v>1.2600126001274248E-3</v>
       </c>
-      <c r="L74">
-        <f t="shared" si="3"/>
-        <v>4.7822503297098748</v>
-      </c>
-      <c r="M74" s="2">
-        <f t="shared" si="2"/>
-        <v>1.1000110001013752E-4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M74" s="2"/>
+      <c r="N74">
+        <f>AVERAGE(L74:L78)</f>
+        <v>3.4578189169508007</v>
+      </c>
+      <c r="O74" s="2">
+        <f>AVERAGE(M74:M78)</f>
+        <v>1.000010000128763E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -3115,11 +3108,11 @@
         <v>3.3987992839800194</v>
       </c>
       <c r="M75" s="2">
-        <f t="shared" ref="M75:M78" si="4">E75-C75</f>
+        <f t="shared" ref="M75:M77" si="4">E75-C75</f>
         <v>1.0000100001050782E-4</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>13</v>
       </c>
@@ -3150,16 +3143,9 @@
       <c r="J76">
         <v>1.2000120001189885E-3</v>
       </c>
-      <c r="L76">
-        <f t="shared" si="3"/>
-        <v>4.4250021039253404</v>
-      </c>
-      <c r="M76" s="2">
-        <f t="shared" si="4"/>
-        <v>1.2000120001687264E-4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="M76" s="2"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -3199,7 +3185,7 @@
         <v>1.0000100000695511E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -3239,12 +3225,12 @@
         <v>1.0000100002116596E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -3283,8 +3269,16 @@
         <f>E80-C80</f>
         <v>1.6800168001669391E-3</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N80">
+        <f>AVERAGE(L80:L84)</f>
+        <v>1.9115520166989026</v>
+      </c>
+      <c r="O80" s="2">
+        <f>AVERAGE(M80:M84)</f>
+        <v>1.6860168601684933E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -3324,7 +3318,7 @@
         <v>1.7000170001679749E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -3364,7 +3358,7 @@
         <v>1.6800168001722682E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -3404,7 +3398,7 @@
         <v>1.6600166001694561E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -3444,12 +3438,12 @@
         <v>1.7100171001658282E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -3488,8 +3482,16 @@
         <f>E86-C86</f>
         <v>1.5900159001596137E-3</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N86">
+        <f>AVERAGE(L86:L90)</f>
+        <v>3.9803189174894813</v>
+      </c>
+      <c r="O86" s="2">
+        <f>AVERAGE(M86:M90)</f>
+        <v>4.0200402004018085E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -3529,7 +3531,7 @@
         <v>1.0000100001050782E-4</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -3569,7 +3571,7 @@
         <v>1.1000110001191388E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -3609,7 +3611,7 @@
         <v>1.1000110001191388E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -3649,12 +3651,12 @@
         <v>1.0000100000695511E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>16</v>
       </c>
@@ -3693,8 +3695,16 @@
         <f>E92-C92</f>
         <v>1.7500175001750051E-3</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N92">
+        <f>AVERAGE(L92:L96)</f>
+        <v>2.1589852188619298</v>
+      </c>
+      <c r="O92" s="2">
+        <f>AVERAGE(M92:M96)</f>
+        <v>1.750017500173584E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -3734,7 +3744,7 @@
         <v>1.720017200170787E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -3774,7 +3784,7 @@
         <v>1.7000170001679749E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3814,7 +3824,7 @@
         <v>1.7900179001770766E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3854,12 +3864,12 @@
         <v>1.7900179001770766E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -3898,8 +3908,16 @@
         <f>E98-C98</f>
         <v>1.6000160001539143E-3</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N98">
+        <f>AVERAGE(L98:L103)</f>
+        <v>3.1502065263277697</v>
+      </c>
+      <c r="O98">
+        <f>AVERAGE(M98:M103)</f>
+        <v>1.5783491168169423E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -3939,7 +3957,7 @@
         <v>1.6000160001539143E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -3979,7 +3997,7 @@
         <v>1.5300153001476247E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -4019,7 +4037,7 @@
         <v>1.5300153001476247E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -4059,7 +4077,7 @@
         <v>1.620016200149621E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -4099,7 +4117,7 @@
         <v>1.5900159001489556E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>2</v>
       </c>
